--- a/Result/profitability/3266.xlsx
+++ b/Result/profitability/3266.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2987500000000001</v>
+        <v>0.2762500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>32.55625000000001</v>
+        <v>30.51875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2850000000000001</v>
+        <v>0.09375000000000003</v>
       </c>
       <c r="N3" t="n">
-        <v>34.8275</v>
+        <v>31.4925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09750000000000003</v>
+        <v>0.08250000000000003</v>
       </c>
       <c r="N4" t="n">
-        <v>35.4675</v>
+        <v>32.70875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08000000000000003</v>
+        <v>0.06125000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>36.3075</v>
+        <v>34.3475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07000000000000003</v>
+        <v>0.05500000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>37.94875</v>
+        <v>35.52625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06375000000000003</v>
+        <v>0.01625000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>39.56</v>
+        <v>35.42125</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02500000000000003</v>
+        <v>0.003750000000000026</v>
       </c>
       <c r="N8" t="n">
-        <v>39.55</v>
+        <v>37.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9796,6 +9796,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3266</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>515</v>
+      </c>
+      <c r="D75" t="n">
+        <v>469</v>
+      </c>
+      <c r="E75" t="n">
+        <v>46</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.16%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2812500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.6825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.416666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6461780929866037</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-15.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6358475263584753</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
